--- a/assets/downloads/sap-lead-assessment-master.xlsx
+++ b/assets/downloads/sap-lead-assessment-master.xlsx
@@ -147,7 +147,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9">
@@ -167,7 +167,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
@@ -188,7 +188,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.6%</t>
+          <t xml:space="preserve">34.8%</t>
         </is>
       </c>
     </row>
@@ -18468,42 +18468,42 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/</t>
+          <t xml:space="preserve">/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/index.md</t>
+          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-memory, integration-cleancore</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -18521,7 +18521,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -18533,42 +18533,42 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
+          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">/labs/</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
+          <t xml:space="preserve">labs/index.md</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, delivery-memory, integration-cleancore</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -18586,7 +18586,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -18603,17 +18603,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
+          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -18651,7 +18651,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -18668,17 +18668,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
+          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -18733,17 +18733,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
+          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
+          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -18798,17 +18798,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
+          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -18858,22 +18858,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI / RAG / Agents</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
+          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -18888,7 +18888,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
+          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -18923,42 +18923,42 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">AI / RAG / Agents</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/</t>
+          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -18976,7 +18976,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -18993,37 +18993,37 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
+          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/index.md</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -19058,17 +19058,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
+          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -19123,37 +19123,37 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -19171,7 +19171,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -19188,17 +19188,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -19218,7 +19218,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, ai-readiness, delivery-testing</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -19253,17 +19253,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
+          <t xml:space="preserve">lead-evidence, ai-readiness, delivery-testing</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -19301,7 +19301,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -19318,17 +19318,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -19383,17 +19383,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -19413,7 +19413,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -19448,37 +19448,37 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
+          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -19496,7 +19496,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -19508,37 +19508,37 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
+          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -19548,7 +19548,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J241" t="n">
@@ -19561,7 +19561,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -19573,27 +19573,27 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Templates / Work Artifacts</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/</t>
+          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/index.md</t>
+          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -19613,7 +19613,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J242" t="n">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -19638,37 +19638,37 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Templates / Work Artifacts</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">/labs/templates/</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+          <t xml:space="preserve">labs/templates/index.md</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">excluded</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -19703,70 +19703,135 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
+          <t xml:space="preserve">Assessment Practice</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">excluded</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="J244" t="n">
+        <v>1</v>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tooling / Roadmap</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B245" t="inlineStr">
         <is>
           <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
+      <c r="C245" t="inlineStr">
         <is>
           <t xml:space="preserve">/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="D245" t="inlineStr">
         <is>
           <t xml:space="preserve">labs/tool-roadmap/index.md</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
+      <c r="E245" t="inlineStr">
         <is>
           <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
+      <c r="F245" t="inlineStr">
         <is>
           <t xml:space="preserve">undeclared</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
+      <c r="G245" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
         <is>
           <t xml:space="preserve">delivery-testing, ai-agents-mcp, ai-data-governance</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="J244" t="n">
-        <v>1</v>
-      </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Started</t>
-        </is>
-      </c>
-      <c r="L244" t="inlineStr">
+      <c r="I245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J245" t="n">
+        <v>1</v>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
         <is>
           <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="M244" t="inlineStr">
+      <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M244"/>
+  <autoFilter ref="A1:M245"/>
 </worksheet>
 </file>
 
@@ -20552,10 +20617,10 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F35" t="n">
         <v>21</v>

--- a/assets/downloads/sap-lead-assessment-master.xlsx
+++ b/assets/downloads/sap-lead-assessment-master.xlsx
@@ -147,7 +147,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9">
@@ -167,7 +167,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
@@ -188,7 +188,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.8%</t>
+          <t xml:space="preserve">35.1%</t>
         </is>
       </c>
     </row>
@@ -12683,42 +12683,42 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRFplus, AIF and ISLM — Decision, Recovery and AI Lifecycle</t>
+          <t xml:space="preserve">Payments, Banks and Rejections — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/frameworks/</t>
+          <t xml:space="preserve">/labs/enterprise-context/finance-logistics/payments-banks-rejections/</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/frameworks/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/finance-logistics/payments-banks-rejections/index.md</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, sales-diagnostics, sales-o2c</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-cicd, integration-cleancore</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/frameworks/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/finance-logistics/payments-banks-rejections/</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -12753,17 +12753,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Context Lab — Process, Data, Rules and AI Reasoning</t>
+          <t xml:space="preserve">BRFplus, AIF and ISLM — Decision, Recovery and AI Lifecycle</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/</t>
+          <t xml:space="preserve">/labs/enterprise-context/frameworks/</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/frameworks/index.md</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, delivery-testing, integration-patterns</t>
+          <t xml:space="preserve">delivery-ams, delivery-cicd, integration-cleancore</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/frameworks/</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -12818,17 +12818,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Industry Solutions — Enterprise Context Lab</t>
+          <t xml:space="preserve">Enterprise Context Lab — Process, Data, Rules and AI Reasoning</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/industries/</t>
+          <t xml:space="preserve">/labs/enterprise-context/</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/industries/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/index.md</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality, ai-readiness, delivery-observability</t>
+          <t xml:space="preserve">integration-ownership, delivery-testing, integration-patterns</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/industries/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -12878,27 +12878,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Operations</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Operations</t>
+          <t xml:space="preserve">SAP Industry Solutions — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/integration-operations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/industries/</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/integration-operations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/industries/index.md</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-recovery</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-production-quality, ai-readiness, delivery-observability</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integration-operations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/industries/</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -12943,27 +12943,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">Integration Operations</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data Migration</t>
+          <t xml:space="preserve">Integration Operations</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/integrations/data-migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/integration-operations/</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/integrations/data-migration/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/integration-operations/index.html</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -12973,12 +12973,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, integration-recovery</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/data-migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integration-operations/</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -13013,37 +13013,37 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP DRF — Data Replication Framework</t>
+          <t xml:space="preserve">Data Migration</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/integrations/drf/</t>
+          <t xml:space="preserve">/labs/enterprise-context/integrations/data-migration/</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/integrations/drf/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/integrations/data-migration/index.html</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/drf/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/data-migration/</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -13078,17 +13078,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Integration Architecture — Logistics, Events and Data Distribution</t>
+          <t xml:space="preserve">SAP DRF — Data Replication Framework</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/integrations/drf/</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/integrations/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/integrations/drf/index.md</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -13098,12 +13098,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -13126,7 +13126,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/drf/</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -13138,22 +13138,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Inventory Management</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inventory Management</t>
+          <t xml:space="preserve">SAP Integration Architecture — Logistics, Events and Data Distribution</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/inventory-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/integrations/</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/inventory-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/integrations/index.md</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-inventory</t>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/inventory-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/integrations/</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -13203,27 +13203,27 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Inventory Management</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iot Devices</t>
+          <t xml:space="preserve">Inventory Management</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/iot-devices/</t>
+          <t xml:space="preserve">/labs/enterprise-context/inventory-management/</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/iot-devices/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/inventory-management/index.html</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-inventory</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J144" t="n">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/iot-devices/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/inventory-management/</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -13268,27 +13268,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Kanban</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Cycle</t>
+          <t xml:space="preserve">Iot Devices</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/control-cycle/</t>
+          <t xml:space="preserve">/labs/enterprise-context/iot-devices/</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/control-cycle/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/iot-devices/index.html</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/control-cycle/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/iot-devices/</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13338,17 +13338,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kanban</t>
+          <t xml:space="preserve">Control Cycle</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/control-cycle/</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/control-cycle/index.html</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/control-cycle/</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -13403,17 +13403,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operations Diagnostics</t>
+          <t xml:space="preserve">Kanban</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/operations-diagnostics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/operations-diagnostics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/index.html</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-inventory</t>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J147" t="n">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/operations-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -13468,17 +13468,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull Control</t>
+          <t xml:space="preserve">Operations Diagnostics</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/pull-control/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/operations-diagnostics/</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/pull-control/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/operations-diagnostics/index.html</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13493,7 +13493,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve">logistics-inventory</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J148" t="n">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/pull-control/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/operations-diagnostics/</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -13533,17 +13533,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Replenishment Strategies</t>
+          <t xml:space="preserve">Pull Control</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/replenishment-strategies/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/pull-control/</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/replenishment-strategies/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/pull-control/index.html</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p</t>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/replenishment-strategies/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/pull-control/</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -13598,17 +13598,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Runtime Flows</t>
+          <t xml:space="preserve">Replenishment Strategies</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/runtime-flows/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/replenishment-strategies/</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/runtime-flows/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/replenishment-strategies/index.html</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13646,7 +13646,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/runtime-flows/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/replenishment-strategies/</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -13663,17 +13663,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Statuses Signals</t>
+          <t xml:space="preserve">Runtime Flows</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/kanban/statuses-signals/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/runtime-flows/</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/kanban/statuses-signals/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/runtime-flows/index.html</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13688,7 +13688,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-inventory</t>
+          <t xml:space="preserve">logistics-p2p</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/statuses-signals/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/runtime-flows/</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -13723,22 +13723,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">SAP Kanban</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logistics Capabilities</t>
+          <t xml:space="preserve">Statuses Signals</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/logistics-capabilities/</t>
+          <t xml:space="preserve">/labs/enterprise-context/kanban/statuses-signals/</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/logistics-capabilities/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/kanban/statuses-signals/index.html</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership</t>
+          <t xml:space="preserve">logistics-inventory</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/logistics-capabilities/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/kanban/statuses-signals/</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -13788,22 +13788,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Data</t>
+          <t xml:space="preserve">Logistics Capabilities</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/master-data/</t>
+          <t xml:space="preserve">/labs/enterprise-context/logistics-capabilities/</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/master-data/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/logistics-capabilities/index.html</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data</t>
+          <t xml:space="preserve">integration-ownership</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J153" t="n">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/logistics-capabilities/</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -13858,17 +13858,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Material Behavior</t>
+          <t xml:space="preserve">Master Data</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/material-behavior/</t>
+          <t xml:space="preserve">/labs/enterprise-context/master-data/</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/material-behavior/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/master-data/index.html</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13906,7 +13906,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/material-behavior/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/master-data/</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -13918,27 +13918,27 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Solution Architecture — Enterprise Context Lab</t>
+          <t xml:space="preserve">Material Behavior</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/architecture/</t>
+          <t xml:space="preserve">/labs/enterprise-context/material-behavior/</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/architecture/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/material-behavior/index.html</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -13948,12 +13948,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, logistics-mdg, ai-data-governance</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/architecture/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/material-behavior/</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -13988,37 +13988,37 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Lead Assessment Drills — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Solution Architecture — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/assessment/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/architecture/</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/assessment/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/architecture/index.md</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, lead-decision, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-recovery, logistics-mdg, ai-data-governance</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -14036,7 +14036,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/assessment/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/architecture/</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -14053,37 +14053,37 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Build &amp; Runtime Anatomy — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Lead Assessment Drills — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/build-runtime/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/assessment/</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/build-runtime/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/assessment/index.md</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-recovery, lead-decision, logistics-mdg</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-cicd, lead-decision, ai-business-value</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -14101,7 +14101,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/build-runtime/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/assessment/</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -14118,37 +14118,37 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Consolidation &amp; Golden Record — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Build &amp; Runtime Anatomy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/consolidation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/build-runtime/</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/consolidation/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/build-runtime/index.md</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-cicd, lead-decision, ai-business-value</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/consolidation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/build-runtime/</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -14183,17 +14183,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Matching &amp; Survivorship — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Consolidation &amp; Golden Record — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/consolidation/survivorship/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/consolidation/</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/consolidation/survivorship/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/consolidation/index.md</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/consolidation/survivorship/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/consolidation/</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -14248,37 +14248,37 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Data Model Engineering — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Matching &amp; Survivorship — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/engineering/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/consolidation/survivorship/</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/data-model/engineering/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/consolidation/survivorship/index.md</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, delivery-testing, ai-readiness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/engineering/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/consolidation/survivorship/</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -14313,17 +14313,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Data Model Anatomy — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Data Model Engineering — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/engineering/</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/data-model/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/data-model/engineering/index.md</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, ai-readiness</t>
+          <t xml:space="preserve">logistics-mdg, delivery-testing, ai-readiness</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/engineering/</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -14378,17 +14378,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Deployment Options — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Data Model Anatomy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/deployments/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/data-model/</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/deployments/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/data-model/index.md</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14408,12 +14408,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-deployment, lead-decision, integration-cleancore</t>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, ai-readiness</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -14426,7 +14426,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/deployments/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/data-model/</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -14438,22 +14438,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner / CVI</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Business Partner Entity Map — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Deployment Options — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/deployments/</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/business-partner/entity-map/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/deployments/index.md</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-observability, delivery-release, integration-deployment</t>
+          <t xml:space="preserve">integration-deployment, lead-decision, integration-cleancore</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J163" t="n">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/deployments/</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -14508,37 +14508,37 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Business Partner, Customer &amp; Supplier — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Business Partner Entity Map — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/business-partner/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/business-partner/entity-map/index.md</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-observability, delivery-release, integration-deployment</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/entity-map/</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -14568,22 +14568,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">Business Partner / CVI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Domain Engineering — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Business Partner, Customer &amp; Supplier — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/business-partner/</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/business-partner/index.md</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg, sales-o2c</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -14621,7 +14621,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/business-partner/</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -14638,42 +14638,42 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Material Entity Map — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Domain Engineering — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/entity-map/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/material/entity-map/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/index.md</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-observability, integration-ownership</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/entity-map/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -14703,42 +14703,42 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Material Domain — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Material Entity Map — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/entity-map/</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/domains/material/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/material/entity-map/index.md</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-observability, integration-ownership</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/entity-map/</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -14768,37 +14768,37 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Extension Matrix — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Material Domain — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/extensions/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/domains/material/</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/extensions/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/domains/material/index.md</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-cleancore, integration-deployment, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/extensions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/domains/material/</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -14833,17 +14833,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG BRFplus Rule Catalog — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Extension Matrix — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/extensions/</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/brfplus-rules/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/extensions/index.md</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14863,7 +14863,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve">integration-cleancore, integration-deployment, delivery-testing</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/extensions/</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -14898,37 +14898,37 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Change Request Type Matrix — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG BRFplus Rule Catalog — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/change-request-matrix/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/change-request-matrix/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/brfplus-rules/index.md</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-decision, logistics-master-data, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/change-request-matrix/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/brfplus-rules/</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -14963,17 +14963,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Governance Engine — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Change Request Type Matrix — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/change-request-matrix/</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/change-request-matrix/index.md</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -15011,7 +15011,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/change-request-matrix/</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -15028,37 +15028,37 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDG Attribute to Process Impact — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Governance Engine — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/impact/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/governance-engine/</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/impact/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/governance-engine/index.md</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">lead-decision, logistics-master-data, logistics-mdg</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, delivery-testing, integration-ownership</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/impact/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/governance-engine/</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -15093,17 +15093,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Implementation and Presales Guide — Enterprise Context Lab</t>
+          <t xml:space="preserve">MDG Attribute to Process Impact — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/implementation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/impact/</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/implementation/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/impact/index.md</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -15123,12 +15123,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-ownership</t>
+          <t xml:space="preserve">sales-o2c, delivery-testing, integration-ownership</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J173" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/implementation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/impact/</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -15153,27 +15153,27 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data Governance</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data Governance — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Implementation and Presales Guide — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/implementation/</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/implementation/index.md</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -15183,17 +15183,17 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-deployment, integration-ownership</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J174" t="n">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/implementation/</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -15218,27 +15218,27 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">Data Governance</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Interface Contracts — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP Master Data Governance — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/interfaces/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/interfaces/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/index.md</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -15248,17 +15248,17 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, logistics-mdg, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J175" t="n">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/interfaces/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -15288,17 +15288,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Lineage &amp; Provenance — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Interface Contracts — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/lineage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/interfaces/</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/lineage/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/interfaces/index.md</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -15318,7 +15318,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, ai-business-value, ai-data-governance</t>
+          <t xml:space="preserve">integration-patterns, logistics-mdg, delivery-testing</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/lineage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/interfaces/</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -15348,22 +15348,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Logistics</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Logistics End-to-End Cases — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Lineage &amp; Provenance — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/cases/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/lineage/</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/logistics/cases/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/lineage/index.md</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-lifecycle, logistics-ewm</t>
+          <t xml:space="preserve">logistics-mdg, ai-business-value, ai-data-governance</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/cases/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/lineage/</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -15418,17 +15418,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG for Logistics — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Logistics End-to-End Cases — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/cases/</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/logistics/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/logistics/cases/index.md</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-tm</t>
+          <t xml:space="preserve">logistics-tm, delivery-lifecycle, logistics-ewm</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/cases/</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -15478,22 +15478,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG / DRF</t>
+          <t xml:space="preserve">SAP Logistics</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Migration &amp; Load Strategy — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG for Logistics — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/logistics/</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/migration/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/logistics/index.md</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, ai-readiness, delivery-testing</t>
+          <t xml:space="preserve">sales-o2c, logistics-master-data, logistics-tm</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -15531,7 +15531,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/logistics/</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -15548,17 +15548,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDG Ownership and Federation — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Migration &amp; Load Strategy — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/ownership/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/migration/</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/ownership/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/migration/index.md</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -15578,7 +15578,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, ai-readiness, logistics-mdg</t>
+          <t xml:space="preserve">delivery-release, ai-readiness, delivery-testing</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/ownership/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/migration/</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -15613,17 +15613,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Governance Processes and Tools — Enterprise Context Lab</t>
+          <t xml:space="preserve">MDG Ownership and Federation — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/processes/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/ownership/</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/processes/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/ownership/index.md</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -15643,12 +15643,12 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, ai-data-governance, ai-agents-mcp</t>
+          <t xml:space="preserve">logistics-p2p, ai-readiness, logistics-mdg</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J181" t="n">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/ownership/</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -15678,17 +15678,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Assessment Reasoning — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Governance Processes and Tools — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/reasoning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/processes/</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/reasoning/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/processes/index.md</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -15708,12 +15708,12 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, delivery-testing, ai-agents-mcp</t>
+          <t xml:space="preserve">logistics-mdg, ai-data-governance, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J182" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/reasoning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/processes/</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -15743,37 +15743,37 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Replication &amp; Distribution — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Assessment Reasoning — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/replication/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/reasoning/</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/replication/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/reasoning/index.md</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-lifecycle, delivery-testing, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/replication/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/reasoning/</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -15808,17 +15808,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG DRF Operations &amp; Replay — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG Replication &amp; Distribution — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/replication/operations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/replication/</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/replication/operations/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/replication/index.md</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -15833,7 +15833,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -15856,7 +15856,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/replication/operations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/replication/</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -15873,37 +15873,37 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP MDG Synthetic Material Scenario — Enterprise Context Lab</t>
+          <t xml:space="preserve">SAP MDG DRF Operations &amp; Replay — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/mdg/scenario/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/replication/operations/</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/mdg/scenario/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/replication/operations/index.md</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg, integration-ownership, logistics-master-data</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/scenario/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/replication/operations/</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -15933,42 +15933,42 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Migration</t>
+          <t xml:space="preserve">SAP MDG / DRF</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA API-Led Migration — Design, Restart and Cutover</t>
+          <t xml:space="preserve">SAP MDG Synthetic Material Scenario — Enterprise Context Lab</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/api-led-migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/mdg/scenario/</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/api-led-migration.md</t>
+          <t xml:space="preserve">labs/enterprise-context/mdg/scenario/index.md</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-patterns, integration-recovery</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg, integration-ownership, logistics-master-data</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/api-led-migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/mdg/scenario/</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -16003,17 +16003,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Cutover — Rehearsal, Delta and Reconciliation</t>
+          <t xml:space="preserve">SAP S/4HANA API-Led Migration — Design, Restart and Cutover</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/cutover/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/api-led-migration/</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/cutover.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/api-led-migration.md</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -16028,7 +16028,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-recovery, logistics-inventory</t>
+          <t xml:space="preserve">delivery-release, integration-patterns, integration-recovery</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/cutover/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/api-led-migration/</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -16068,17 +16068,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Design Register — Object Control</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Cutover — Rehearsal, Delta and Reconciliation</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/design-register/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/cutover/</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/design-register.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/cutover.md</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-deployment, lead-decision</t>
+          <t xml:space="preserve">delivery-release, integration-recovery, logistics-inventory</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -16116,7 +16116,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/design-register/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/cutover/</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -16133,17 +16133,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Domain Playbooks — SD, MM, PP, EWM, FI and CO</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Design Register — Object Control</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/domain-playbooks/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/design-register/</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/domain-playbooks.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/design-register.md</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p, logistics-production-quality, sales-o2c</t>
+          <t xml:space="preserve">delivery-release, integration-deployment, lead-decision</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -16181,7 +16181,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/domain-playbooks/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/design-register/</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -16198,17 +16198,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Greenfield Migration — Architecture and Data Load</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Domain Playbooks — SD, MM, PP, EWM, FI and CO</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/domain-playbooks/</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/domain-playbooks.md</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-deployment, logistics-master-data</t>
+          <t xml:space="preserve">logistics-p2p, logistics-production-quality, sales-o2c</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -16246,7 +16246,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/domain-playbooks/</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -16263,17 +16263,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Lead Assessment — Architecture Drills</t>
+          <t xml:space="preserve">SAP S/4HANA Greenfield Migration — Architecture and Data Load</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/lead-assessment/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/lead-assessment.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/index.md</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -16288,7 +16288,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-deployment, lead-decision</t>
+          <t xml:space="preserve">delivery-release, integration-deployment, logistics-master-data</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/lead-assessment/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -16328,17 +16328,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Factory — Governance, Mock Cycles and Ownership</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Lead Assessment — Architecture Drills</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/migration-factory/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/lead-assessment/</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/migration-factory.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/lead-assessment.md</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -16353,7 +16353,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-release, integration-recovery, lead-decision</t>
+          <t xml:space="preserve">delivery-release, integration-deployment, lead-decision</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -16376,7 +16376,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/migration-factory/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/lead-assessment/</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -16393,17 +16393,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Object Catalog — Greenfield Load Scope</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Factory — Governance, Mock Cycles and Ownership</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/object-catalog/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/migration-factory/</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/object-catalog.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/migration-factory.md</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -16418,7 +16418,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-master-data, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">delivery-release, integration-recovery, lead-decision</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -16441,7 +16441,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/object-catalog/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/migration-factory/</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -16458,17 +16458,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA Migration Tools — Cockpit, APIs and Integration</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Object Catalog — Greenfield Load Scope</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/migration/tooling/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/object-catalog/</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/migration/tooling.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/object-catalog.md</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -16483,7 +16483,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-cicd, integration-deployment, integration-patterns</t>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -16506,7 +16506,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/tooling/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/object-catalog/</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -16518,47 +16518,47 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Migration</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterprise Context Lab — Model and Authoring Contract</t>
+          <t xml:space="preserve">SAP S/4HANA Migration Tools — Cockpit, APIs and Integration</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/model/</t>
+          <t xml:space="preserve">/labs/enterprise-context/migration/tooling/</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/model/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/migration/tooling.md</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-cicd, integration-deployment, integration-patterns</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-data-governance, ai-retrieval, delivery-cicd</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J195" t="n">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/model/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/migration/tooling/</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -16583,47 +16583,47 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Performance</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Performance and Technical Operations — Practical S/4HANA Troubleshooting</t>
+          <t xml:space="preserve">Enterprise Context Lab — Model and Authoring Contract</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/performance/</t>
+          <t xml:space="preserve">/labs/enterprise-context/model/</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/performance/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/model/index.md</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-observability, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-data-governance, ai-retrieval, delivery-cicd</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J196" t="n">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/performance/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/model/</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -16648,42 +16648,42 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Pricing</t>
+          <t xml:space="preserve">SAP Performance</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anatomy</t>
+          <t xml:space="preserve">SAP Performance and Technical Operations — Practical S/4HANA Troubleshooting</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/anatomy/</t>
+          <t xml:space="preserve">/labs/enterprise-context/performance/</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/anatomy/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/performance/index.md</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-observability, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/anatomy/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/performance/</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -16718,17 +16718,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casebook</t>
+          <t xml:space="preserve">Anatomy</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/casebook/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/anatomy/</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/casebook/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/anatomy/index.html</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/casebook/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/anatomy/</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -16783,17 +16783,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configuration</t>
+          <t xml:space="preserve">Casebook</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/configuration/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/casebook/</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/configuration/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/casebook/index.html</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing, delivery-testing, integration-development</t>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/configuration/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/casebook/</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -16848,22 +16848,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pricing</t>
+          <t xml:space="preserve">Configuration</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/configuration/</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/configuration/index.html</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -16873,12 +16873,12 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-pricing, delivery-testing, integration-development</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -16896,7 +16896,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/configuration/</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -16913,22 +16913,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operations</t>
+          <t xml:space="preserve">Pricing</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/operations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/operations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/index.html</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -16938,12 +16938,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, integration-deployment, integration-recovery</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -16961,7 +16961,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/operations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -16978,17 +16978,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scenarios</t>
+          <t xml:space="preserve">Operations</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/pricing/scenarios/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/operations/</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/pricing/scenarios/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/operations/index.html</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -17008,7 +17008,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-pricing</t>
+          <t xml:space="preserve">delivery-ams, integration-deployment, integration-recovery</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/scenarios/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/operations/</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -17038,27 +17038,27 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Procurement / MM</t>
+          <t xml:space="preserve">SAP Pricing</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procurement</t>
+          <t xml:space="preserve">Scenarios</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/procurement/</t>
+          <t xml:space="preserve">/labs/enterprise-context/pricing/scenarios/</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/procurement/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/pricing/scenarios/index.html</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -17068,12 +17068,12 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-p2p</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-pricing</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/pricing/scenarios/</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -17103,22 +17103,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Production / PP</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production</t>
+          <t xml:space="preserve">Procurement</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/index.html</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -17133,7 +17133,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve">logistics-p2p</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J204" t="n">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -17168,22 +17168,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Quality Management</t>
+          <t xml:space="preserve">SAP Production / PP</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quality Management</t>
+          <t xml:space="preserve">Production</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -17221,7 +17221,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -17233,27 +17233,27 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Quality Management</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
+          <t xml:space="preserve">Quality Management</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -17263,17 +17263,17 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-evaluation, delivery-lifecycle, delivery-release</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J206" t="n">
@@ -17286,7 +17286,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -17298,22 +17298,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytics / Observability</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Analytics</t>
+          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -17333,12 +17333,12 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-evaluation, delivery-lifecycle, delivery-release</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J207" t="n">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -17363,27 +17363,27 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Analytics / Observability</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Diagnostics</t>
+          <t xml:space="preserve">Sales Analytics</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-diagnostics</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -17433,22 +17433,22 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order</t>
+          <t xml:space="preserve">Sales Diagnostics</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -17458,7 +17458,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-diagnostics</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -17481,7 +17481,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -17498,17 +17498,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Plane</t>
+          <t xml:space="preserve">Sales Order</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -17546,7 +17546,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -17563,17 +17563,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Claims</t>
+          <t xml:space="preserve">Control Plane</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -17628,17 +17628,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coverage</t>
+          <t xml:space="preserve">Returns Claims</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -17658,12 +17658,12 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J212" t="n">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -17693,22 +17693,22 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Processes</t>
+          <t xml:space="preserve">Coverage</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -17753,27 +17753,27 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Sales Processes</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -17783,12 +17783,12 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -17806,7 +17806,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -17818,22 +17818,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Data</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -17853,12 +17853,12 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg</t>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J215" t="n">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -17883,22 +17883,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivation</t>
+          <t xml:space="preserve">Master Data</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -17918,12 +17918,12 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J216" t="n">
@@ -17936,7 +17936,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -17953,17 +17953,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanisms</t>
+          <t xml:space="preserve">Derivation</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -18013,27 +18013,27 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Shipping</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shipping</t>
+          <t xml:space="preserve">Mechanisms</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -18043,7 +18043,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-shipping</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -18053,7 +18053,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J218" t="n">
@@ -18066,7 +18066,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -18078,27 +18078,27 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">SAP Shipping</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax</t>
+          <t xml:space="preserve">Shipping</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -18108,7 +18108,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-shipping</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -18118,7 +18118,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J219" t="n">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -18143,37 +18143,37 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Tax</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
+          <t xml:space="preserve">Tax</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -18183,7 +18183,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J220" t="n">
@@ -18196,7 +18196,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -18208,37 +18208,37 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges</t>
+          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -18248,7 +18248,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J221" t="n">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -18278,22 +18278,22 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transportation Management</t>
+          <t xml:space="preserve">Charges</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -18338,27 +18338,27 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Transportation Management</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -18368,17 +18368,17 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J223" t="n">
@@ -18391,7 +18391,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -18403,22 +18403,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planning</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -18438,12 +18438,12 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J224" t="n">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -18468,47 +18468,47 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
+          <t xml:space="preserve">Planning</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J225" t="n">
@@ -18521,7 +18521,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -18533,42 +18533,42 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/</t>
+          <t xml:space="preserve">/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/index.md</t>
+          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-memory, integration-cleancore</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -18586,7 +18586,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -18598,42 +18598,42 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
+          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">/labs/</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
+          <t xml:space="preserve">labs/index.md</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, delivery-memory, integration-cleancore</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -18651,7 +18651,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -18668,17 +18668,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
+          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -18733,17 +18733,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
+          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -18798,17 +18798,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
+          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
+          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -18863,17 +18863,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
+          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -18888,7 +18888,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -18923,22 +18923,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI / RAG / Agents</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
+          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -18953,7 +18953,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
+          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -18976,7 +18976,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -18988,42 +18988,42 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">AI / RAG / Agents</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/</t>
+          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -19058,37 +19058,37 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
+          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/index.md</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -19123,17 +19123,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
+          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -19171,7 +19171,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -19188,37 +19188,37 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -19253,17 +19253,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, ai-readiness, delivery-testing</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -19301,7 +19301,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -19318,17 +19318,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
+          <t xml:space="preserve">lead-evidence, ai-readiness, delivery-testing</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -19383,17 +19383,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -19413,7 +19413,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -19448,17 +19448,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -19478,7 +19478,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -19496,7 +19496,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -19513,37 +19513,37 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
+          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -19561,7 +19561,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -19573,37 +19573,37 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
+          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -19613,7 +19613,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J242" t="n">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -19638,27 +19638,27 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Templates / Work Artifacts</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
+          <t xml:space="preserve">Reusable Data Procedures</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/</t>
+          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/index.md</t>
+          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -19678,7 +19678,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J243" t="n">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -19703,37 +19703,37 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Templates / Work Artifacts</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">/labs/templates/</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+          <t xml:space="preserve">labs/templates/index.md</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">excluded</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -19768,70 +19768,135 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
+          <t xml:space="preserve">Assessment Practice</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">excluded</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="J245" t="n">
+        <v>1</v>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tooling / Roadmap</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B246" t="inlineStr">
         <is>
           <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
+      <c r="C246" t="inlineStr">
         <is>
           <t xml:space="preserve">/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="D246" t="inlineStr">
         <is>
           <t xml:space="preserve">labs/tool-roadmap/index.md</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
+      <c r="E246" t="inlineStr">
         <is>
           <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr">
+      <c r="F246" t="inlineStr">
         <is>
           <t xml:space="preserve">undeclared</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr">
+      <c r="G246" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
         <is>
           <t xml:space="preserve">delivery-testing, ai-agents-mcp, ai-data-governance</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="J245" t="n">
-        <v>1</v>
-      </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Started</t>
-        </is>
-      </c>
-      <c r="L245" t="inlineStr">
+      <c r="I246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J246" t="n">
+        <v>1</v>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
         <is>
           <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="M245" t="inlineStr">
+      <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M245"/>
+  <autoFilter ref="A1:M246"/>
 </worksheet>
 </file>
 
@@ -21145,10 +21210,10 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
         <v>4</v>

--- a/assets/downloads/sap-lead-assessment-master.xlsx
+++ b/assets/downloads/sap-lead-assessment-master.xlsx
@@ -147,7 +147,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9">
@@ -167,7 +167,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -188,7 +188,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">35.1%</t>
+          <t xml:space="preserve">36.4%</t>
         </is>
       </c>
     </row>
@@ -17168,22 +17168,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Production / PP</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production</t>
+          <t xml:space="preserve">Supplier Automatic Payments — F110 and F0770 Lead Lab</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/automatic-payments/index.md</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -17193,12 +17193,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -17208,7 +17208,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J205" t="n">
@@ -17221,7 +17221,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/automatic-payments/</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -17233,22 +17233,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Quality Management</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quality Management</t>
+          <t xml:space="preserve">Supplier Bank Clearing &amp; EBS — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/bank-clearing/index.md</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -17258,12 +17258,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-production-quality</t>
+          <t xml:space="preserve">delivery-ams, integration-observability, integration-recovery</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -17273,7 +17273,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J206" t="n">
@@ -17286,7 +17286,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/bank-clearing/</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -17298,42 +17298,42 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
+          <t xml:space="preserve">Supplier Payments &amp; AP — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/index.md</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-evaluation, delivery-lifecycle, delivery-release</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -17363,37 +17363,37 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analytics / Observability</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Analytics</t>
+          <t xml:space="preserve">Supplier Payment Readiness — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/readiness/</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/readiness/index.md</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-master-data, logistics-p2p</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J208" t="n">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/readiness/</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -17428,22 +17428,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Procurement / MM</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Diagnostics</t>
+          <t xml:space="preserve">Supplier Payment Rejections &amp; Recovery — SAP S/4HANA Lead Lab</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/procurement/suppliers/rejections-recovery/index.md</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -17453,12 +17453,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-diagnostics</t>
+          <t xml:space="preserve">delivery-ams, integration-recovery, logistics-p2p</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -17468,7 +17468,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J209" t="n">
@@ -17481,7 +17481,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/procurement/suppliers/rejections-recovery/</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -17493,27 +17493,27 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Production / PP</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Order</t>
+          <t xml:space="preserve">Production</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/production/index.html</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -17546,7 +17546,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/production/</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -17558,27 +17558,27 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">SAP Quality Management</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control Plane</t>
+          <t xml:space="preserve">Quality Management</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/quality-management/index.html</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -17588,7 +17588,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-production-quality</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/quality-management/</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -17623,22 +17623,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Returns Claims</t>
+          <t xml:space="preserve">SAP S/4HANA 2025 Release Readiness Playbook</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/release-readiness/index.md</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -17658,12 +17658,12 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ai-evaluation, delivery-lifecycle, delivery-release</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J212" t="n">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/release-readiness/</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -17688,22 +17688,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Sales / SD</t>
+          <t xml:space="preserve">Analytics / Observability</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coverage</t>
+          <t xml:space="preserve">Sales Analytics</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-analytics/index.html</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -17723,12 +17723,12 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J213" t="n">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-analytics/</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -17758,17 +17758,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Processes</t>
+          <t xml:space="preserve">Sales Diagnostics</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-diagnostics/index.html</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -17783,7 +17783,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-o2c</t>
+          <t xml:space="preserve">sales-diagnostics</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -17793,7 +17793,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J214" t="n">
@@ -17806,7 +17806,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-diagnostics/</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -17818,22 +17818,22 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Sales Order</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-order/index.html</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -17853,12 +17853,12 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J215" t="n">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-order/</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -17883,22 +17883,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Master Data</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Data</t>
+          <t xml:space="preserve">Control Plane</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/index.html</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -17918,12 +17918,12 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-mdg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J216" t="n">
@@ -17936,7 +17936,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -17953,17 +17953,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivation</t>
+          <t xml:space="preserve">Returns Claims</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/control-plane/returns-claims/index.html</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/control-plane/returns-claims/</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -18018,17 +18018,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanisms</t>
+          <t xml:space="preserve">Coverage</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/coverage/index.html</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -18048,12 +18048,12 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-testing, lead-evidence, lead-readiness</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J218" t="n">
@@ -18066,7 +18066,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/coverage/</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -18078,22 +18078,22 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Shipping</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shipping</t>
+          <t xml:space="preserve">Sales Processes</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/index.html</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -18108,7 +18108,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">sales-shipping</t>
+          <t xml:space="preserve">sales-o2c</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -18143,22 +18143,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Tax</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tax</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/integrations/index.html</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -18178,12 +18178,12 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J220" t="n">
@@ -18196,7 +18196,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/integrations/</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -18208,47 +18208,47 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other / Cross-domain</t>
+          <t xml:space="preserve">SAP Master Data</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
+          <t xml:space="preserve">Master Data</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/master-data/index.html</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-mdg</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="J221" t="n">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/master-data/</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -18273,22 +18273,22 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges</t>
+          <t xml:space="preserve">Derivation</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/derivation/index.html</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/derivation/</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -18338,27 +18338,27 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">SAP Sales / SD</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transportation Management</t>
+          <t xml:space="preserve">Mechanisms</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/sales-processes/mechanisms/index.html</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -18368,7 +18368,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -18391,7 +18391,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/sales-processes/mechanisms/</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -18403,27 +18403,27 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integration Architecture</t>
+          <t xml:space="preserve">SAP Shipping</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integrations</t>
+          <t xml:space="preserve">Shipping</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/shipping/index.html</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -18433,12 +18433,12 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">sales-shipping</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/shipping/</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -18468,22 +18468,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP TM</t>
+          <t xml:space="preserve">SAP Tax</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planning</t>
+          <t xml:space="preserve">Tax</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
+          <t xml:space="preserve">labs/enterprise-context/tax/index.html</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -18521,7 +18521,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/tax/</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -18538,17 +18538,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
+          <t xml:space="preserve">SAP Testing Strategy for S/4HANA Delivery</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/testing/index.md</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
+          <t xml:space="preserve">delivery-lifecycle, delivery-testing</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -18586,7 +18586,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/testing/</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -18598,22 +18598,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
+          <t xml:space="preserve">Charges</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/charges/index.html</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -18633,12 +18633,12 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, delivery-memory, integration-cleancore</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J227" t="n">
@@ -18651,7 +18651,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/charges/</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -18663,22 +18663,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
+          <t xml:space="preserve">Transportation Management</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/index.html</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -18688,12 +18688,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -18703,7 +18703,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J228" t="n">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -18728,42 +18728,42 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Integration Architecture</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
+          <t xml:space="preserve">Integrations</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/integrations/index.html</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/integrations/</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -18793,47 +18793,47 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">SAP TM</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
+          <t xml:space="preserve">Planning</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
+          <t xml:space="preserve">labs/enterprise-context/transportation-management/planning/index.html</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J230" t="n">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/enterprise-context/transportation-management/planning/</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -18858,22 +18858,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Other / Cross-domain</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
+          <t xml:space="preserve">SAP Incident Diagnostics — Evidence to Incident Brief and RCA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
+          <t xml:space="preserve">labs/incident-diagnostics/index.md</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -18888,7 +18888,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
+          <t xml:space="preserve">integration-observability, integration-recovery, logistics-mdg</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/incident-diagnostics/</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -18923,42 +18923,42 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">Assessment Practice</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
+          <t xml:space="preserve">Labs — SAP Enterprise, Assurance, AI, Interview and Assessment</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">/labs/</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
+          <t xml:space="preserve">labs/index.md</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, delivery-memory, integration-cleancore</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -18976,7 +18976,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -18988,22 +18988,22 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI / RAG / Agents</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
+          <t xml:space="preserve">SAP Lead Boss Battles — Long-form Interview Pressure Cases</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/boss-battles/index.md</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -19018,7 +19018,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
+          <t xml:space="preserve">ai-readiness, integration-ownership, lead-answer, lead-challenge, lead-decision, lead-stakeholders, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/boss-battles/</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -19058,37 +19058,37 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
+          <t xml:space="preserve">SAP Lead Contrast Lab — Distinguish the Right Boundary</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/</t>
+          <t xml:space="preserve">/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/contrast/index.md</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/contrast/</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -19123,17 +19123,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
+          <t xml:space="preserve">SAP Lead Decision Cards — Architecture Trade-offs for Interviews</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/decision-cards/index.md</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve">ai-readiness, integration-patterns, integration-recovery, lead-challenge, lead-decision, logistics-ewm</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -19171,7 +19171,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/decision-cards/</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -19188,17 +19188,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
+          <t xml:space="preserve">SAP Lead Diagnostic Lab — Production Failure Scenarios</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/diagnostic-lab/index.md</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -19213,7 +19213,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
+          <t xml:space="preserve">delivery-testing, integration-recovery, logistics-inventory, sales-atp, sales-billing, sales-diagnostics</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/diagnostic-lab/</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -19253,37 +19253,37 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
+          <t xml:space="preserve">SAP Lead Interview Drills — Decisions, Diagnostics, Pressure, Evidence</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/drills/index.md</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">lead-answer, lead-challenge, lead-decision, lead-evidence</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -19301,7 +19301,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/drills/</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -19313,42 +19313,42 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interview Readiness</t>
+          <t xml:space="preserve">AI / RAG / Agents</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
+          <t xml:space="preserve">SAP Lead Evidence Bank — Project Story Coverage</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/evidence-bank/index.md</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-ownership, lead-decision, lead-evidence, lead-stakeholders</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, ai-readiness, delivery-testing</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/evidence-bank/</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -19383,17 +19383,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
+          <t xml:space="preserve">SAP Lead Interview Readiness — Practical Preparation Lab</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/index.md</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -19413,7 +19413,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
+          <t xml:space="preserve">delivery-ams, logistics-tm, sales-shipping</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -19448,37 +19448,37 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
+          <t xml:space="preserve">SAP Lead Learning Science — Evidence Learning Engine</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/learning-science/index.md</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -19496,7 +19496,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/learning-science/</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -19513,37 +19513,37 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+          <t xml:space="preserve">SAP Lead Memory Atlas — Rebuild O2C, P2P and Integration</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/memory-atlas/index.md</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">needs_decision</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">undeclared</t>
+          <t xml:space="preserve">mapped</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">integration-patterns, integration-recovery, logistics-p2p, sales-o2c</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -19561,7 +19561,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/memory-atlas/</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -19578,37 +19578,37 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
+          <t xml:space="preserve">SAP Lead Interview Practice — 12-Question Interview Mode</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/practice/index.md</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/practice/</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -19638,22 +19638,22 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reusable Data Procedures</t>
+          <t xml:space="preserve">SAP Lead Interview Progress — Readiness and Weak Areas</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
+          <t xml:space="preserve">labs/interview-readiness/progress/index.md</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">lead-evidence, ai-readiness, delivery-testing</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J243" t="n">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/progress/</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -19703,27 +19703,27 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Templates / Work Artifacts</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
+          <t xml:space="preserve">SAP Lead Interview Questions — 42 Skills, 168 Questions</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/</t>
+          <t xml:space="preserve">/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/index.md</t>
+          <t xml:space="preserve">labs/interview-readiness/questions/index.md</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapped</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -19733,17 +19733,17 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery-memory</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">logistics-tm, delivery-ams, integration-ownership</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J244" t="n">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/questions/</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -19768,32 +19768,32 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assessment Practice</t>
+          <t xml:space="preserve">Interview Readiness</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+          <t xml:space="preserve">SAP Lead Career Roadmap — Skills, Labs, Evidence, Practice</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+          <t xml:space="preserve">labs/interview-readiness/roadmap/index.md</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">excluded</t>
+          <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">undeclared</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -19803,12 +19803,12 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery-ams, logistics-tm, delivery-lifecycle</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="J245" t="n">
@@ -19821,7 +19821,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/roadmap/</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -19833,70 +19833,395 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Interview Story Bank — Projects, Decisions, Failures, Results</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/stories/</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/stories/index.md</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_decision</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undeclared</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lead-evidence, integration-deployment, ai-agents-mcp</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J246" t="n">
+        <v>1</v>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/stories/</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Interview Readiness</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Mastery Today — Recall, Apply, Retain</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/interview-readiness/today/</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/interview-readiness/today/index.md</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery-memory, delivery-testing, lead-answer</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J247" t="n">
+        <v>1</v>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/interview-readiness/today/</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reusable Data Procedures</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reusable Data Procedures</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/reusable-data-procedures/</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/reusable-data-procedures/index.html</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">needs_decision</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undeclared</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="J248" t="n">
+        <v>1</v>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/reusable-data-procedures/</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Templates / Work Artifacts</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operational Templates — RCA and Procedures</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/templates/</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/templates/index.md</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapped</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undeclared</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery-memory</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="J249" t="n">
+        <v>1</v>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assessment Practice</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAP Lead Assessment Master Workbook</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">labs/templates/sap-lead-assessment-prep.md</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">excluded</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="J250" t="n">
+        <v>1</v>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://dkharlanau.github.io/labs/templates/sap-lead-assessment-prep/</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tooling / Roadmap</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="B251" t="inlineStr">
         <is>
           <t xml:space="preserve">Tool Roadmap — Portable Enterprise Tools</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
+      <c r="C251" t="inlineStr">
         <is>
           <t xml:space="preserve">/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
+      <c r="D251" t="inlineStr">
         <is>
           <t xml:space="preserve">labs/tool-roadmap/index.md</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
+      <c r="E251" t="inlineStr">
         <is>
           <t xml:space="preserve">needs_decision</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
+      <c r="F251" t="inlineStr">
         <is>
           <t xml:space="preserve">undeclared</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
+      <c r="G251" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
         <is>
           <t xml:space="preserve">delivery-testing, ai-agents-mcp, ai-data-governance</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="J246" t="n">
-        <v>1</v>
-      </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Started</t>
-        </is>
-      </c>
-      <c r="L246" t="inlineStr">
+      <c r="I251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="J251" t="n">
+        <v>1</v>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Started</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
         <is>
           <t xml:space="preserve">https://dkharlanau.github.io/labs/tool-roadmap/</t>
         </is>
       </c>
-      <c r="M246" t="inlineStr">
+      <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M246"/>
+  <autoFilter ref="A1:M251"/>
 </worksheet>
 </file>
 
@@ -21518,10 +21843,10 @@
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
